--- a/artfynd/A 30617-2024 artfynd.xlsx
+++ b/artfynd/A 30617-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,6 +1252,678 @@
           <t>Stadens biologiska mångfald (LONA)</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118942864</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91065</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>585026</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6577595</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118942892</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100114</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>585026</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6577595</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118943265</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91065</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>585082</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6577573</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118943385</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100114</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>585079</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6577584</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118943555</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>585103</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6577586</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118943023</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100114</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>585045</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6577578</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30617-2024 artfynd.xlsx
+++ b/artfynd/A 30617-2024 artfynd.xlsx
@@ -1367,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118942892</v>
+        <v>118943023</v>
       </c>
       <c r="B8" t="n">
         <v>100114</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585026</v>
+        <v>585045</v>
       </c>
       <c r="R8" t="n">
-        <v>6577595</v>
+        <v>6577578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118943265</v>
+        <v>118943555</v>
       </c>
       <c r="B9" t="n">
-        <v>91065</v>
+        <v>100024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585082</v>
+        <v>585103</v>
       </c>
       <c r="R9" t="n">
-        <v>6577573</v>
+        <v>6577586</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118943385</v>
+        <v>118943265</v>
       </c>
       <c r="B10" t="n">
-        <v>100114</v>
+        <v>91065</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585079</v>
+        <v>585082</v>
       </c>
       <c r="R10" t="n">
-        <v>6577584</v>
+        <v>6577573</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118943555</v>
+        <v>118942892</v>
       </c>
       <c r="B11" t="n">
-        <v>100024</v>
+        <v>100114</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585103</v>
+        <v>585026</v>
       </c>
       <c r="R11" t="n">
-        <v>6577586</v>
+        <v>6577595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118943023</v>
+        <v>118943385</v>
       </c>
       <c r="B12" t="n">
         <v>100114</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585045</v>
+        <v>585079</v>
       </c>
       <c r="R12" t="n">
-        <v>6577578</v>
+        <v>6577584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 30617-2024 artfynd.xlsx
+++ b/artfynd/A 30617-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1925,6 +1925,1195 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118983248</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>585099</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6577544</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118982724</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>585068</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6577537</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118983765</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>585117</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6577574</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118982751</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100114</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>585084</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6577539</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118981533</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>585028</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6577555</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118984147</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100114</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>585141</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6577577</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118983003</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90511</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>585035</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6577546</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118983467</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>585135</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6577581</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118984221</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91065</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>585159</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6577583</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118983147</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90511</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skogstorp (Skogstorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>585030</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6577527</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30617-2024 artfynd.xlsx
+++ b/artfynd/A 30617-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118942864</v>
+        <v>118943023</v>
       </c>
       <c r="B7" t="n">
-        <v>91065</v>
+        <v>100114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3884</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585026</v>
+        <v>585045</v>
       </c>
       <c r="R7" t="n">
-        <v>6577595</v>
+        <v>6577578</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21:33</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>21:33</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118943023</v>
+        <v>118943555</v>
       </c>
       <c r="B8" t="n">
-        <v>100114</v>
+        <v>100024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585045</v>
+        <v>585103</v>
       </c>
       <c r="R8" t="n">
-        <v>6577578</v>
+        <v>6577586</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118943555</v>
+        <v>118943265</v>
       </c>
       <c r="B9" t="n">
-        <v>100024</v>
+        <v>91065</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585103</v>
+        <v>585082</v>
       </c>
       <c r="R9" t="n">
-        <v>6577586</v>
+        <v>6577573</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:23</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118943265</v>
+        <v>118942892</v>
       </c>
       <c r="B10" t="n">
-        <v>91065</v>
+        <v>100114</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3884</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585082</v>
+        <v>585026</v>
       </c>
       <c r="R10" t="n">
-        <v>6577573</v>
+        <v>6577595</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118942892</v>
+        <v>118942864</v>
       </c>
       <c r="B11" t="n">
-        <v>100114</v>
+        <v>91065</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118983248</v>
+        <v>118983147</v>
       </c>
       <c r="B13" t="n">
-        <v>57306</v>
+        <v>90511</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,42 +1943,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogstorp (Skogstorp), Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585099</v>
+        <v>585030</v>
       </c>
       <c r="R13" t="n">
-        <v>6577544</v>
+        <v>6577527</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,6 +2023,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2044,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118982724</v>
+        <v>118983467</v>
       </c>
       <c r="B14" t="n">
-        <v>100024</v>
+        <v>57306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,35 +2071,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2093,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585068</v>
+        <v>585135</v>
       </c>
       <c r="R14" t="n">
-        <v>6577537</v>
+        <v>6577581</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118983765</v>
+        <v>118982724</v>
       </c>
       <c r="B15" t="n">
-        <v>57306</v>
+        <v>100024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,31 +2188,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2210,10 +2225,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585117</v>
+        <v>585068</v>
       </c>
       <c r="R15" t="n">
-        <v>6577574</v>
+        <v>6577537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118982751</v>
+        <v>118983003</v>
       </c>
       <c r="B16" t="n">
-        <v>100114</v>
+        <v>90511</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,25 +2309,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2322,13 +2337,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585084</v>
+        <v>585035</v>
       </c>
       <c r="R16" t="n">
-        <v>6577539</v>
+        <v>6577546</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2357,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,6 +2393,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2394,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118981533</v>
+        <v>118982751</v>
       </c>
       <c r="B17" t="n">
-        <v>57306</v>
+        <v>100114</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,46 +2441,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogstorp (Skogstorp), Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585028</v>
+        <v>585084</v>
       </c>
       <c r="R17" t="n">
-        <v>6577555</v>
+        <v>6577539</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2474,7 +2504,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2514,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118984147</v>
+        <v>118983765</v>
       </c>
       <c r="B18" t="n">
-        <v>100114</v>
+        <v>57306</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,38 +2553,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogstorp (Skogstorp), Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585141</v>
+        <v>585117</v>
       </c>
       <c r="R18" t="n">
-        <v>6577577</v>
+        <v>6577574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2631,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118983003</v>
+        <v>118984147</v>
       </c>
       <c r="B19" t="n">
-        <v>90511</v>
+        <v>100114</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,25 +2670,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,13 +2698,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585035</v>
+        <v>585141</v>
       </c>
       <c r="R19" t="n">
-        <v>6577546</v>
+        <v>6577577</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,26 +2754,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2755,7 +2770,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118983467</v>
+        <v>118981533</v>
       </c>
       <c r="B20" t="n">
         <v>57306</v>
@@ -2791,7 +2806,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2800,13 +2815,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585135</v>
+        <v>585028</v>
       </c>
       <c r="R20" t="n">
-        <v>6577581</v>
+        <v>6577555</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2835,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118984221</v>
+        <v>118983248</v>
       </c>
       <c r="B21" t="n">
-        <v>91065</v>
+        <v>57306</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,41 +2899,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3884</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogstorp (Skogstorp), Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585159</v>
+        <v>585099</v>
       </c>
       <c r="R21" t="n">
-        <v>6577583</v>
+        <v>6577544</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2947,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2977,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +3004,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118983147</v>
+        <v>118984221</v>
       </c>
       <c r="B22" t="n">
-        <v>90511</v>
+        <v>91065</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,25 +3016,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>3884</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3024,13 +3044,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585030</v>
+        <v>585159</v>
       </c>
       <c r="R22" t="n">
-        <v>6577527</v>
+        <v>6577583</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3059,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +3089,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,26 +3100,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
